--- a/consent_forms/032_online_poll_participation_consent_form--consent_forms.xlsx
+++ b/consent_forms/032_online_poll_participation_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>has_participant_id</t>
+          <t>has_participant_id_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>has participant id</t>
+          <t>Has Participant Id 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>participant_id_type</t>
+          <t>participant_id_type_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>participant id type</t>
+          <t>Participant Id Type 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>has_first_name</t>
+          <t>has_first_name_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>has first name</t>
+          <t>Has First Name 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>first_name_type</t>
+          <t>first_name_type_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>first name type</t>
+          <t>First Name Type 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>has_email</t>
+          <t>has_email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>has email</t>
+          <t>Has Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>email_type</t>
+          <t>email_type_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>email type</t>
+          <t>Email Type 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>has_phone_number</t>
+          <t>has_phone_number_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>has phone number</t>
+          <t>Has Phone Number 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>participant_id_type</t>
+          <t>participant_id_type_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>participant id type</t>
+          <t>Participant Id Type 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>has_participant_id_choices</t>
+          <t>has_participant_id_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>has_participant_id_choices</t>
+          <t>has_participant_id_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>participant_id_type_choices</t>
+          <t>participant_id_type_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>participant_id_type_choices</t>
+          <t>participant_id_type_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>has_first_name_choices</t>
+          <t>has_first_name_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>has_first_name_choices</t>
+          <t>has_first_name_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>first_name_type_choices</t>
+          <t>first_name_type_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>first_name_type_choices</t>
+          <t>first_name_type_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>has_email_choices</t>
+          <t>has_email_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>has_email_choices</t>
+          <t>has_email_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>email_type_choices</t>
+          <t>email_type_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>email_type_choices</t>
+          <t>email_type_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>has_phone_number_choices</t>
+          <t>has_phone_number_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>has_phone_number_choices</t>
+          <t>has_phone_number_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>participant_id_type_choices</t>
+          <t>participant_id_type_3_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>participant_id_type_choices</t>
+          <t>participant_id_type_3_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
